--- a/산출물/API_목록_Running_Coach_v2.0.xlsx
+++ b/산출물/API_목록_Running_Coach_v2.0.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Garmin &amp; Stat Service" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -840,4 +841,170 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>서비스 명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>HTTP Method</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>API Endpoint</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기능 명</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>상세 설명 및 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Garmin Service</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>/api/v1/garmin/connect</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Garmin 계정 최초 연동 및 세션 생성</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ID/PW 검증 후 OAuth2 세션 토큰 저장 및 GARMIN_ACCOUNT_LINK 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Garmin Service</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>/api/v1/garmin/sync-initial/{runner_id}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>과거 전체 데이터 선택적 초기 동기화</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>마이페이지 버튼 클릭 시 과거 전체 러닝 기록 배치 페이징 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Garmin Service</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>/api/v1/garmin/sync-recent/{runner_id}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>최근 데이터 증분 수동 동기화</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>대시보드/리스트 새로고침 시 last_synced_at 이후 최근 N개 핀포인트 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Stat Service</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>/health</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FastAPI 마이크로서비스 헬스체크</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>stat_service 통계 및 가민 서비스 가동 상태 확인</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>